--- a/resampling/input/accessibility_reports_returned/IMC_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/IMC_accessibility_report.xlsx
@@ -197,8 +197,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:Q45" headerRowCount="1">
-  <autoFilter ref="A1:Q34"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:Q70" headerRowCount="1">
+  <autoFilter ref="A1:Q70"/>
   <tableColumns count="17">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
@@ -704,7 +704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q45"/>
+  <dimension ref="A1:Q70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14" customWidth="1" style="11" min="1" max="2"/>
@@ -914,12 +914,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>N/A - fully accessible</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Partially accessible - some areas could not be reached. See Cluster Accessibility for the specific clusters affected.</t>
+          <t>60% accessible where we've collected places</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1366,12 +1366,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Insecurity / conflict</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Area inaccessible because of insecurity and safety concerns.</t>
+          <t>is in Damboa not in Chibok and is inaccessible</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -1611,17 +1611,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Insecurity / conflict</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Partially accessible - some areas could not be reached. See Cluster Accessibility for the specific clusters affected.</t>
+          <t>IMC cant cover this area</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t xml:space="preserve">partially accessible with high risk </t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-08-23 - IMC confirmed by email (RE IMC Accessibility Report, 23/08): non_idp_NG021020_2 is Not Accessible (corrects the earlier submitted cluster sheet, which had said Accessible) - so only the IDP cluster is accessible, matching IMC's original ward-level narrative. Confirmed: idp_NG021020_2 (12 HHs) Accessible/completed; non_idp_NG021020_1 (3 of its 6 HHs fall in this ward), non_idp_NG021020_2 (6 HHs), non_idp_NG021020_4 (6 HHs) all Not Accessible. One further gap found independently while reconciling this (not something IMC was asked about): non_idp_NG021020_3 has 2 primary HHs in this ward that never appeared in IMC's pre-fix template at all - still needs separate confirmation. Achieved = 12/29 (41%) confirmed accessible; remainder needs resampling/follow-up on the 2 confirmed-inaccessible clusters, plus a check on the 2-HH gap.</t>
+          <t>accessible where IDP resides / main town</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -2375,12 +2375,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>partially accessible  with high risk</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Consistent across both IMC documents (point-level review and template).</t>
+          <t>Fakuwa and Kafin Dangi are two different community but merged in one LGAs</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>almost inaccessible (jungle)</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2431,12 +2436,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>partially accessible  with high risk</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Point-level file (20/08) showed this fully Not Accessible; IMC's own template (21/08) reports Yes/partial - "only 5 HH were accessible due to insecurity." User decision 2026-08-22: follow the template, flagged for follow-up and partial resample. Recomputed against the CORRECTED target for this ward (9 HH, not the pre-fix 12 IMC's own 42% was computed against): cluster non_idp_NG021020_14 (2 of its primary HHs fall in this ward) = Accessible; non_idp_NG021020_5 (6 HHs) = Not Accessible/insecurity. A third cluster, non_idp_NG021020_7 (1 HH here), didn't exist as part of this ward in IMC's pre-fix template at all and was never reviewed - needs separate confirmation. Achieved = 2/9 (22%) confirmed accessible; remainder (7 HH) needs resampling/follow-up.</t>
+          <t>It's a big ward and only the town by the road is accessible</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -2679,12 +2684,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Insecurity / conflict</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2804,17 +2809,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Insecurity / conflict</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Newly-added ward following the 2026-08-21 ward-splitting fix - did not exist as its own row when IMC's original files were generated. Confirmed directly accessible with the IMC team, 2026-08-22.</t>
+          <t>it falled under  Dutsin-Ma LGA (not part of Kankia LGA)</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2870,12 +2875,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Insecurity / conflict</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3308,7 +3313,6 @@
           <t>Boko</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3351,7 +3355,6 @@
           <t>Yashe B</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3378,23 +3381,1042 @@
       </c>
       <c r="O45" s="12" t="n"/>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Chibok</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Gumsuri</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Chibok</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Hausari Zadawa</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Askira/Uba</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Chibok</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Mussa</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Askira/Uba</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Chibok</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Nzuba Wayaram</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Buni Gari</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Biu</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Dalwa</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Jere; Konduga</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Foi</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Kaga; Konduga</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Goneri</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Kaga</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Gulak</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Gur</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Biu</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Kautikari</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Askira/Uba; Chibok</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Mallumdunari</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Mboakura</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Chibok</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ngulde</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Askira/Uba; Biu; Chibok; Hawul</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ngurthavu Kopa</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Askira/Uba</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Doka</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Bindawa; Charanchi; Danja; Rimi</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Duddunni</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Bindawa; Kusada</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Gaiwa</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Bindawa</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Garu</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Musawa</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Kamri</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Bindawa; Charanchi</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Karaduwa</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Matazu; Musawa</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Koda</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Charanchi</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Kuki A</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Charanchi; Dutsin-Ma; Matazu</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Radda</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Charanchi; Dutsin-Ma</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Yankamaye</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Kusada</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="K2:K34 K35:K39 K40:K45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L34 L35:L39 L40:L45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L2:L70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P34 P35:P39 P40:P45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:Q34 Q35:Q39 Q40:Q45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Q2:Q70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="O35:O39 O40:O45" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today." type="date" operator="between">
+    <dataValidation sqref="O2:O70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-09-16</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7873,8 +8895,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064B5BF8B0F90A143B1A4ACAD04008153" ma:contentTypeVersion="15" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="7a2915931200ea69f6d4702d545d15c4">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="30973102-2308-455b-8e1f-b6a90edc3b23" xmlns:ns3="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ebf5164e0bbea30cbcbeb97056918f83" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064B5BF8B0F90A143B1A4ACAD04008153" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada0274d0d067bbbdece3301958c05ce">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="30973102-2308-455b-8e1f-b6a90edc3b23" xmlns:ns3="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f05eaaac1f596f0cf4554f8e9f637ce" ns2:_="" ns3:_="">
     <xsd:import namespace="30973102-2308-455b-8e1f-b6a90edc3b23"/>
     <xsd:import namespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1"/>
     <xsd:element name="properties">
@@ -7922,7 +8944,7 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Balises d’images" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -7981,7 +9003,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Partagé avec" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -8000,7 +9022,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Partagé avec détails" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -8017,8 +9039,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Type de contenu"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titre"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -8128,13 +9150,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B4170BC-2A2E-4EDB-B0B2-5DE76D3CBDE4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38BEA453-534F-407B-80F2-2212080754C2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16353E4F-E7CD-407E-B4DE-5126B200CB2B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D610971A-D538-4686-8D57-281FCE870044}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5C3B335-599F-4437-82BA-72B2CFBB3419}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A121EE-27C7-46D4-8CFF-B3BE3BDF4A7B}"/>
 </file>
--- a/resampling/input/accessibility_reports_returned/IMC_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/IMC_accessibility_report.xlsx
@@ -223,8 +223,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O70" headerRowCount="1">
-  <autoFilter ref="A1:O70"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O124" headerRowCount="1">
+  <autoFilter ref="A1:O124"/>
   <tableColumns count="15">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
@@ -4432,7 +4432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O70"/>
+  <dimension ref="A1:O124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14" customWidth="1" style="11" min="1" max="2"/>
@@ -8872,18 +8872,2166 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Kafa Mafi</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>non_idp_NG008007_supp1</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Chibok</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Whuntaku</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>non_idp_NG008006_supp2</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Chibok</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Mbalala</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>non_idp_NG008006_supp3</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Chibok</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Whuntaku</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>non_idp_NG008006_supp4</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Chibok</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Mbalala</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>non_idp_NG008006_supp5</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Chibok</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Whuntaku</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>non_idp_NG008006_supp6</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Chibok</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Likama</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>non_idp_NG008006_supp7</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Chibok</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ngohi</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>non_idp_NG008006_supp8</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Chibok</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ngulde</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>non_idp_NG008006_supp9</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Mulgoi Kobchi</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>non_idp_NG008007_supp3</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Bego Yerwa</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>non_idp_NG008007_supp5</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Bita Izge</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>non_idp_NG008007_supp6</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Bego Yerwa</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>non_idp_NG008007_supp9</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Fakuwa Kafin Dangi</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>non_idp_NG021020_supp1</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Tafashiya Nasarawa</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>non_idp_NG021020_supp3</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Chibok</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Whuntaku</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>non_idp_NG008006_supp10</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Chibok</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ngohi</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>non_idp_NG008006_supp11</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ajigin B</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>non_idp_NG008007_supp10</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Yashe B</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>non_idp_NG021020_supp4</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Fakuwa Kafin Dangi</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>non_idp_NG021020_supp5</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Fakuwa Kafin Dangi</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>non_idp_NG021020_supp6</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Boko</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>non_idp_NG021020_supp7</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Galadima B</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>non_idp_NG021020_supp8</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Kafa Mafi</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>non_idp_NG008007_supp13</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Tafashiya Nasarawa</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>non_idp_NG021020_supp10</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Kafa Mafi</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>non_idp_NG008007_supp15</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Mulgoi Kobchi</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>non_idp_NG008007_supp14</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Bita Izge</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>non_idp_NG008007_supp17</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Bego Yerwa</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>non_idp_NG008007_supp18</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Mulgoi Kobchi</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>non_idp_NG008007_supp20</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Chibok</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Mboakura</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>idp_NG008006_supp1</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Chibok</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Mboakura</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>idp_NG008006_supp2</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Chibok</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Whuntaku</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>idp_NG008006_supp3</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Chibok</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Whuntaku</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>idp_NG008006_supp4</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Chibok</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Mbalala</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>idp_NG008006_supp5</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Chibok</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Whuntaku</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>idp_NG008006_supp6</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Chibok</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Garu</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>idp_NG008006_supp7</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Chibok</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Likama</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>idp_NG008006_supp8</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Chibok</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Garu</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>idp_NG008006_supp9</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>idp_NG008007_supp10</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>idp_NG008007_supp11</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>idp_NG008007_supp12</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>idp_NG008007_supp2</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>idp_NG008007_supp5</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>idp_NG008007_supp6</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>idp_NG008007_supp7</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>idp_NG008007_supp8</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>idp_NG008007_supp9</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Tafashiya Nasarawa</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>idp_NG021020_supp1</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Galadima B</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>idp_NG021020_supp2</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Gachi</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>idp_NG021020_supp3</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Gachi</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>idp_NG021020_supp4</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Galadima B</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>idp_NG021020_supp5</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Kankia</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Galadima A</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>idp_NG021020_supp6</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="I2:I70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I124" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J124" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N124" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O124" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9150,13 +11298,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38BEA453-534F-407B-80F2-2212080754C2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D251991-81E8-460A-AF3D-B48A4B9BF6B3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D610971A-D538-4686-8D57-281FCE870044}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BC4DD81-B6FB-4357-AABA-8CD6FF5F8030}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A121EE-27C7-46D4-8CFF-B3BE3BDF4A7B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A17B69E7-9A5E-4D56-A97B-32622F526244}"/>
 </file>
--- a/resampling/input/accessibility_reports_returned/IMC_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/IMC_accessibility_report.xlsx
@@ -11040,271 +11040,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064B5BF8B0F90A143B1A4ACAD04008153" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada0274d0d067bbbdece3301958c05ce">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="30973102-2308-455b-8e1f-b6a90edc3b23" xmlns:ns3="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f05eaaac1f596f0cf4554f8e9f637ce" ns2:_="" ns3:_="">
-    <xsd:import namespace="30973102-2308-455b-8e1f-b6a90edc3b23"/>
-    <xsd:import namespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="30973102-2308-455b-8e1f-b6a90edc3b23" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="22" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="13" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{daf5bdda-bc47-491d-9935-b3e42d5c0ae4}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="947c1918-d5ab-48a1-8b61-0d52f2f99fd1">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="30973102-2308-455b-8e1f-b6a90edc3b23">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D251991-81E8-460A-AF3D-B48A4B9BF6B3}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BC4DD81-B6FB-4357-AABA-8CD6FF5F8030}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A17B69E7-9A5E-4D56-A97B-32622F526244}"/>
 </file>
--- a/resampling/input/accessibility_reports_returned/IMC_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/IMC_accessibility_report.xlsx
@@ -11040,4 +11040,271 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064B5BF8B0F90A143B1A4ACAD04008153" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada0274d0d067bbbdece3301958c05ce">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="30973102-2308-455b-8e1f-b6a90edc3b23" xmlns:ns3="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f05eaaac1f596f0cf4554f8e9f637ce" ns2:_="" ns3:_="">
+    <xsd:import namespace="30973102-2308-455b-8e1f-b6a90edc3b23"/>
+    <xsd:import namespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="30973102-2308-455b-8e1f-b6a90edc3b23" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="22" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="13" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{daf5bdda-bc47-491d-9935-b3e42d5c0ae4}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="947c1918-d5ab-48a1-8b61-0d52f2f99fd1">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="30973102-2308-455b-8e1f-b6a90edc3b23">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1E9DC21-C628-4A05-B193-CCA342243CE2}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{280614BC-8924-4A64-BB22-A03C6576AF49}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C9171A7-4355-4717-A5D5-83A7F1416B29}"/>
 </file>